--- a/reports/SQZ6_202606.xlsx
+++ b/reports/SQZ6_202606.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Daily Breakdown'!$A$1:$U$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Entry Detail'!$A$2:$V$554</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Per-Entry Detail'!$A$2:$V$570</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -620,10 +620,10 @@
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
@@ -785,7 +785,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-22 20:47:00</t>
+          <t>2026-06-22 22:07:00</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$13,028.91</t>
+          <t>$12,849.56</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$-471.09</t>
+          <t>$-650.44</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$-485.97</t>
+          <t>$-666.04</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$14.88</t>
+          <t>$15.60</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-4.82%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-6.39%</t>
+          <t>-7.71%</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
@@ -887,7 +887,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25 / 35</t>
+          <t>26 / 37</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>41.67%</t>
+          <t>41.27%</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -980,11 +980,11 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
     </row>
@@ -1025,11 +1025,11 @@
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
     </row>
     <row r="39"/>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>512</v>
+        <v>528</v>
       </c>
     </row>
     <row r="42">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>281</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1:1.00</t>
+          <t>1:1.01</t>
         </is>
       </c>
     </row>
@@ -1214,41 +1214,41 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>-485.9742857142419</v>
+        <v>-666.044285714238</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>14.88000000000001</v>
+        <v>15.60000000000001</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>4.960000000000003</v>
+        <v>5.200000000000003</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>-471.0942857142417</v>
+        <v>-650.4442857142377</v>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="M51" s="14" t="n">
-        <v>13028.90571428575</v>
+        <v>12849.55571428575</v>
       </c>
     </row>
   </sheetData>
@@ -1287,10 +1287,10 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
     <col width="8" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
@@ -1410,37 +1410,37 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>40</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>66</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>19</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
@@ -1453,28 +1453,28 @@
         </is>
       </c>
       <c r="O2" s="10" t="n">
-        <v>-485.9742857142419</v>
+        <v>-666.044285714238</v>
       </c>
       <c r="P2" s="11" t="n">
-        <v>14.88000000000001</v>
+        <v>15.60000000000001</v>
       </c>
       <c r="Q2" s="12" t="n">
-        <v>4.960000000000003</v>
+        <v>5.200000000000003</v>
       </c>
       <c r="R2" s="10" t="n">
-        <v>-471.0942857142417</v>
+        <v>-650.4442857142377</v>
       </c>
       <c r="S2" s="13" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="T2" s="14" t="n">
-        <v>13028.90571428575</v>
+        <v>12849.55571428575</v>
       </c>
       <c r="U2" s="13" t="inlineStr">
         <is>
-          <t>-3.49%</t>
+          <t>-4.82%</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V554"/>
+  <dimension ref="A1:V570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -43955,7 +43955,7 @@
       </c>
       <c r="P490" s="9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TIME_EXIT</t>
         </is>
       </c>
       <c r="Q490" s="9" t="inlineStr">
@@ -43963,15 +43963,27 @@
           <t>2026-06-22 17:20</t>
         </is>
       </c>
-      <c r="R490" s="9" t="n"/>
-      <c r="S490" s="34" t="n"/>
-      <c r="T490" s="51" t="n"/>
+      <c r="R490" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:15</t>
+        </is>
+      </c>
+      <c r="S490" s="34" t="n">
+        <v>4186.53</v>
+      </c>
+      <c r="T490" s="36" t="n">
+        <v>-6.470000000000255</v>
+      </c>
       <c r="U490" s="37" t="inlineStr">
         <is>
           <t>1:2.3</t>
         </is>
       </c>
-      <c r="V490" s="52" t="n"/>
+      <c r="V490" s="38" t="inlineStr">
+        <is>
+          <t>-0.3R</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="26" t="inlineStr">
@@ -46721,37 +46733,49 @@
       <c r="K523" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L523" s="34" t="n">
+      <c r="L523" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M523" s="34" t="n">
+      <c r="M523" s="29" t="n">
         <v>4184</v>
       </c>
-      <c r="N523" s="34" t="n">
+      <c r="N523" s="29" t="n">
         <v>4175.6</v>
       </c>
-      <c r="O523" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P523" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q523" s="9" t="inlineStr">
+      <c r="O523" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P523" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q523" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:29</t>
         </is>
       </c>
-      <c r="R523" s="9" t="n"/>
-      <c r="S523" s="34" t="n"/>
-      <c r="T523" s="51" t="n"/>
-      <c r="U523" s="37" t="inlineStr">
+      <c r="R523" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S523" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T523" s="31" t="n">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="U523" s="32" t="inlineStr">
         <is>
           <t>1:1.9</t>
         </is>
       </c>
-      <c r="V523" s="52" t="n"/>
+      <c r="V523" s="33" t="inlineStr">
+        <is>
+          <t>1:0.83</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="26" t="inlineStr">
@@ -46797,37 +46821,49 @@
       <c r="K524" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L524" s="34" t="n">
+      <c r="L524" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M524" s="34" t="n">
+      <c r="M524" s="29" t="n">
         <v>4183.5</v>
       </c>
-      <c r="N524" s="34" t="n">
+      <c r="N524" s="29" t="n">
         <v>4175.1</v>
       </c>
-      <c r="O524" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P524" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q524" s="9" t="inlineStr">
+      <c r="O524" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P524" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q524" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:29</t>
         </is>
       </c>
-      <c r="R524" s="9" t="n"/>
-      <c r="S524" s="34" t="n"/>
-      <c r="T524" s="51" t="n"/>
-      <c r="U524" s="37" t="inlineStr">
+      <c r="R524" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S524" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T524" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U524" s="32" t="inlineStr">
         <is>
           <t>1:2.0</t>
         </is>
       </c>
-      <c r="V524" s="52" t="n"/>
+      <c r="V524" s="33" t="inlineStr">
+        <is>
+          <t>1:0.89</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="26" t="inlineStr">
@@ -46873,37 +46909,49 @@
       <c r="K525" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L525" s="34" t="n">
+      <c r="L525" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M525" s="34" t="n">
+      <c r="M525" s="29" t="n">
         <v>4183</v>
       </c>
-      <c r="N525" s="34" t="n">
+      <c r="N525" s="29" t="n">
         <v>4174.6</v>
       </c>
-      <c r="O525" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P525" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q525" s="9" t="inlineStr">
+      <c r="O525" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P525" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q525" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:31</t>
         </is>
       </c>
-      <c r="R525" s="9" t="n"/>
-      <c r="S525" s="34" t="n"/>
-      <c r="T525" s="51" t="n"/>
-      <c r="U525" s="37" t="inlineStr">
+      <c r="R525" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S525" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T525" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="U525" s="32" t="inlineStr">
         <is>
           <t>1:2.0</t>
         </is>
       </c>
-      <c r="V525" s="52" t="n"/>
+      <c r="V525" s="33" t="inlineStr">
+        <is>
+          <t>1:0.95</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="26" t="inlineStr">
@@ -46949,37 +46997,49 @@
       <c r="K526" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L526" s="34" t="n">
+      <c r="L526" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M526" s="34" t="n">
+      <c r="M526" s="29" t="n">
         <v>4182.5</v>
       </c>
-      <c r="N526" s="34" t="n">
+      <c r="N526" s="29" t="n">
         <v>4174.1</v>
       </c>
-      <c r="O526" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P526" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q526" s="9" t="inlineStr">
+      <c r="O526" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P526" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q526" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:31</t>
         </is>
       </c>
-      <c r="R526" s="9" t="n"/>
-      <c r="S526" s="34" t="n"/>
-      <c r="T526" s="51" t="n"/>
-      <c r="U526" s="37" t="inlineStr">
+      <c r="R526" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S526" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T526" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U526" s="32" t="inlineStr">
         <is>
           <t>1:2.1</t>
         </is>
       </c>
-      <c r="V526" s="52" t="n"/>
+      <c r="V526" s="33" t="inlineStr">
+        <is>
+          <t>1:1.01</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="26" t="inlineStr">
@@ -47025,37 +47085,49 @@
       <c r="K527" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L527" s="34" t="n">
+      <c r="L527" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M527" s="34" t="n">
+      <c r="M527" s="29" t="n">
         <v>4182</v>
       </c>
-      <c r="N527" s="34" t="n">
+      <c r="N527" s="29" t="n">
         <v>4173.6</v>
       </c>
-      <c r="O527" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P527" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q527" s="9" t="inlineStr">
+      <c r="O527" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P527" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q527" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:32</t>
         </is>
       </c>
-      <c r="R527" s="9" t="n"/>
-      <c r="S527" s="34" t="n"/>
-      <c r="T527" s="51" t="n"/>
-      <c r="U527" s="37" t="inlineStr">
+      <c r="R527" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S527" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T527" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="U527" s="32" t="inlineStr">
         <is>
           <t>1:2.1</t>
         </is>
       </c>
-      <c r="V527" s="52" t="n"/>
+      <c r="V527" s="33" t="inlineStr">
+        <is>
+          <t>1:1.07</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="26" t="inlineStr">
@@ -47101,37 +47173,49 @@
       <c r="K528" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L528" s="34" t="n">
+      <c r="L528" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M528" s="34" t="n">
+      <c r="M528" s="29" t="n">
         <v>4181.5</v>
       </c>
-      <c r="N528" s="34" t="n">
+      <c r="N528" s="29" t="n">
         <v>4173.1</v>
       </c>
-      <c r="O528" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P528" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q528" s="9" t="inlineStr">
+      <c r="O528" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P528" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q528" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:32</t>
         </is>
       </c>
-      <c r="R528" s="9" t="n"/>
-      <c r="S528" s="34" t="n"/>
-      <c r="T528" s="51" t="n"/>
-      <c r="U528" s="37" t="inlineStr">
+      <c r="R528" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S528" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T528" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U528" s="32" t="inlineStr">
         <is>
           <t>1:2.2</t>
         </is>
       </c>
-      <c r="V528" s="52" t="n"/>
+      <c r="V528" s="33" t="inlineStr">
+        <is>
+          <t>1:1.13</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="26" t="inlineStr">
@@ -47177,37 +47261,49 @@
       <c r="K529" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L529" s="34" t="n">
+      <c r="L529" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M529" s="34" t="n">
+      <c r="M529" s="29" t="n">
         <v>4181</v>
       </c>
-      <c r="N529" s="34" t="n">
+      <c r="N529" s="29" t="n">
         <v>4172.6</v>
       </c>
-      <c r="O529" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P529" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q529" s="9" t="inlineStr">
+      <c r="O529" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P529" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q529" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:32</t>
         </is>
       </c>
-      <c r="R529" s="9" t="n"/>
-      <c r="S529" s="34" t="n"/>
-      <c r="T529" s="51" t="n"/>
-      <c r="U529" s="37" t="inlineStr">
+      <c r="R529" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S529" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T529" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="U529" s="32" t="inlineStr">
         <is>
           <t>1:2.3</t>
         </is>
       </c>
-      <c r="V529" s="52" t="n"/>
+      <c r="V529" s="33" t="inlineStr">
+        <is>
+          <t>1:1.19</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="26" t="inlineStr">
@@ -47253,37 +47349,49 @@
       <c r="K530" s="27" t="n">
         <v>4200</v>
       </c>
-      <c r="L530" s="34" t="n">
+      <c r="L530" s="29" t="n">
         <v>4200</v>
       </c>
-      <c r="M530" s="34" t="n">
+      <c r="M530" s="29" t="n">
         <v>4180.5</v>
       </c>
-      <c r="N530" s="34" t="n">
+      <c r="N530" s="29" t="n">
         <v>4172.1</v>
       </c>
-      <c r="O530" s="35" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="P530" s="9" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="Q530" s="9" t="inlineStr">
+      <c r="O530" s="30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P530" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TP2</t>
+        </is>
+      </c>
+      <c r="Q530" s="7" t="inlineStr">
         <is>
           <t>2026-06-22 20:32</t>
         </is>
       </c>
-      <c r="R530" s="9" t="n"/>
-      <c r="S530" s="34" t="n"/>
-      <c r="T530" s="51" t="n"/>
-      <c r="U530" s="37" t="inlineStr">
+      <c r="R530" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:48</t>
+        </is>
+      </c>
+      <c r="S530" s="29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="T530" s="31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U530" s="32" t="inlineStr">
         <is>
           <t>1:2.3</t>
         </is>
       </c>
-      <c r="V530" s="52" t="n"/>
+      <c r="V530" s="33" t="inlineStr">
+        <is>
+          <t>1:1.25</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="26" t="inlineStr">
@@ -49313,8 +49421,1404 @@
       </c>
       <c r="V554" s="52" t="n"/>
     </row>
+    <row r="555">
+      <c r="A555" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.1</t>
+        </is>
+      </c>
+      <c r="B555" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C555" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D555" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E555" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F555" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G555" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H555" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I555" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J555" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K555" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L555" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M555" s="28" t="n">
+        <v>4181</v>
+      </c>
+      <c r="N555" s="28" t="n">
+        <v>4189.4</v>
+      </c>
+      <c r="O555" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P555" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q555" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:53</t>
+        </is>
+      </c>
+      <c r="R555" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:21</t>
+        </is>
+      </c>
+      <c r="S555" s="28" t="n">
+        <v>4189.4</v>
+      </c>
+      <c r="T555" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U555" s="15" t="inlineStr">
+        <is>
+          <t>1:1.9</t>
+        </is>
+      </c>
+      <c r="V555" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.2</t>
+        </is>
+      </c>
+      <c r="B556" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C556" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D556" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E556" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F556" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G556" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H556" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I556" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J556" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K556" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L556" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M556" s="28" t="n">
+        <v>4181.5</v>
+      </c>
+      <c r="N556" s="28" t="n">
+        <v>4189.9</v>
+      </c>
+      <c r="O556" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P556" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q556" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:52</t>
+        </is>
+      </c>
+      <c r="R556" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:21</t>
+        </is>
+      </c>
+      <c r="S556" s="28" t="n">
+        <v>4189.9</v>
+      </c>
+      <c r="T556" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U556" s="15" t="inlineStr">
+        <is>
+          <t>1:2.0</t>
+        </is>
+      </c>
+      <c r="V556" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.3</t>
+        </is>
+      </c>
+      <c r="B557" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C557" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D557" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E557" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F557" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G557" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H557" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I557" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J557" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K557" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L557" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M557" s="28" t="n">
+        <v>4182</v>
+      </c>
+      <c r="N557" s="28" t="n">
+        <v>4190.4</v>
+      </c>
+      <c r="O557" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P557" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q557" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:48</t>
+        </is>
+      </c>
+      <c r="R557" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S557" s="28" t="n">
+        <v>4190.4</v>
+      </c>
+      <c r="T557" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U557" s="15" t="inlineStr">
+        <is>
+          <t>1:2.0</t>
+        </is>
+      </c>
+      <c r="V557" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.4</t>
+        </is>
+      </c>
+      <c r="B558" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C558" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D558" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E558" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F558" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G558" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H558" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I558" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J558" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K558" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L558" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M558" s="28" t="n">
+        <v>4182.5</v>
+      </c>
+      <c r="N558" s="28" t="n">
+        <v>4190.9</v>
+      </c>
+      <c r="O558" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P558" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q558" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:47</t>
+        </is>
+      </c>
+      <c r="R558" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S558" s="28" t="n">
+        <v>4190.9</v>
+      </c>
+      <c r="T558" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U558" s="15" t="inlineStr">
+        <is>
+          <t>1:2.1</t>
+        </is>
+      </c>
+      <c r="V558" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.5</t>
+        </is>
+      </c>
+      <c r="B559" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C559" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D559" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E559" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F559" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G559" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H559" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I559" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J559" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K559" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L559" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M559" s="28" t="n">
+        <v>4183</v>
+      </c>
+      <c r="N559" s="28" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="O559" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P559" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q559" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:47</t>
+        </is>
+      </c>
+      <c r="R559" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S559" s="28" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="T559" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U559" s="15" t="inlineStr">
+        <is>
+          <t>1:2.1</t>
+        </is>
+      </c>
+      <c r="V559" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.6</t>
+        </is>
+      </c>
+      <c r="B560" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C560" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D560" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E560" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F560" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G560" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H560" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I560" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J560" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K560" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L560" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M560" s="28" t="n">
+        <v>4183.5</v>
+      </c>
+      <c r="N560" s="28" t="n">
+        <v>4191.9</v>
+      </c>
+      <c r="O560" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P560" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q560" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:56</t>
+        </is>
+      </c>
+      <c r="R560" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S560" s="28" t="n">
+        <v>4191.9</v>
+      </c>
+      <c r="T560" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U560" s="15" t="inlineStr">
+        <is>
+          <t>1:2.2</t>
+        </is>
+      </c>
+      <c r="V560" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.7</t>
+        </is>
+      </c>
+      <c r="B561" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C561" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D561" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E561" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F561" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G561" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H561" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I561" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J561" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K561" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L561" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M561" s="28" t="n">
+        <v>4184</v>
+      </c>
+      <c r="N561" s="28" t="n">
+        <v>4192.4</v>
+      </c>
+      <c r="O561" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P561" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q561" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:01</t>
+        </is>
+      </c>
+      <c r="R561" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S561" s="28" t="n">
+        <v>4192.4</v>
+      </c>
+      <c r="T561" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U561" s="15" t="inlineStr">
+        <is>
+          <t>1:2.3</t>
+        </is>
+      </c>
+      <c r="V561" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#04.8</t>
+        </is>
+      </c>
+      <c r="B562" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C562" s="26" t="inlineStr">
+        <is>
+          <t>12:45 AM</t>
+        </is>
+      </c>
+      <c r="D562" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:45</t>
+        </is>
+      </c>
+      <c r="E562" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F562" s="27" t="n">
+        <v>4181</v>
+      </c>
+      <c r="G562" s="27" t="n">
+        <v>4183</v>
+      </c>
+      <c r="H562" s="27" t="n">
+        <v>4185</v>
+      </c>
+      <c r="I562" s="27" t="n">
+        <v>4177</v>
+      </c>
+      <c r="J562" s="27" t="n">
+        <v>4173</v>
+      </c>
+      <c r="K562" s="27" t="n">
+        <v>4165</v>
+      </c>
+      <c r="L562" s="28" t="n">
+        <v>4165</v>
+      </c>
+      <c r="M562" s="28" t="n">
+        <v>4184.5</v>
+      </c>
+      <c r="N562" s="28" t="n">
+        <v>4192.9</v>
+      </c>
+      <c r="O562" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P562" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q562" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:01</t>
+        </is>
+      </c>
+      <c r="R562" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S562" s="28" t="n">
+        <v>4192.9</v>
+      </c>
+      <c r="T562" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U562" s="15" t="inlineStr">
+        <is>
+          <t>1:2.3</t>
+        </is>
+      </c>
+      <c r="V562" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.1</t>
+        </is>
+      </c>
+      <c r="B563" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C563" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D563" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E563" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F563" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G563" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H563" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I563" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J563" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K563" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L563" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M563" s="28" t="n">
+        <v>4182</v>
+      </c>
+      <c r="N563" s="28" t="n">
+        <v>4190.4</v>
+      </c>
+      <c r="O563" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P563" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q563" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:54</t>
+        </is>
+      </c>
+      <c r="R563" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S563" s="28" t="n">
+        <v>4190.4</v>
+      </c>
+      <c r="T563" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U563" s="15" t="inlineStr">
+        <is>
+          <t>1:1.9</t>
+        </is>
+      </c>
+      <c r="V563" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.2</t>
+        </is>
+      </c>
+      <c r="B564" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C564" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D564" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E564" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F564" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G564" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H564" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I564" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J564" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K564" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L564" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M564" s="28" t="n">
+        <v>4182.5</v>
+      </c>
+      <c r="N564" s="28" t="n">
+        <v>4190.9</v>
+      </c>
+      <c r="O564" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P564" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q564" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:53</t>
+        </is>
+      </c>
+      <c r="R564" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S564" s="28" t="n">
+        <v>4190.9</v>
+      </c>
+      <c r="T564" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U564" s="15" t="inlineStr">
+        <is>
+          <t>1:2.0</t>
+        </is>
+      </c>
+      <c r="V564" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.3</t>
+        </is>
+      </c>
+      <c r="B565" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C565" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D565" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E565" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F565" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G565" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H565" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I565" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J565" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K565" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L565" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M565" s="28" t="n">
+        <v>4183</v>
+      </c>
+      <c r="N565" s="28" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="O565" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P565" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q565" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:54</t>
+        </is>
+      </c>
+      <c r="R565" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S565" s="28" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="T565" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U565" s="15" t="inlineStr">
+        <is>
+          <t>1:2.0</t>
+        </is>
+      </c>
+      <c r="V565" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.4</t>
+        </is>
+      </c>
+      <c r="B566" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C566" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D566" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E566" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F566" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G566" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H566" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I566" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J566" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K566" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L566" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M566" s="28" t="n">
+        <v>4183.5</v>
+      </c>
+      <c r="N566" s="28" t="n">
+        <v>4191.9</v>
+      </c>
+      <c r="O566" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P566" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q566" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:56</t>
+        </is>
+      </c>
+      <c r="R566" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S566" s="28" t="n">
+        <v>4191.9</v>
+      </c>
+      <c r="T566" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U566" s="15" t="inlineStr">
+        <is>
+          <t>1:2.1</t>
+        </is>
+      </c>
+      <c r="V566" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.5</t>
+        </is>
+      </c>
+      <c r="B567" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C567" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D567" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E567" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F567" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G567" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H567" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I567" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J567" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K567" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L567" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M567" s="28" t="n">
+        <v>4184</v>
+      </c>
+      <c r="N567" s="28" t="n">
+        <v>4192.4</v>
+      </c>
+      <c r="O567" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P567" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q567" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:01</t>
+        </is>
+      </c>
+      <c r="R567" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S567" s="28" t="n">
+        <v>4192.4</v>
+      </c>
+      <c r="T567" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U567" s="15" t="inlineStr">
+        <is>
+          <t>1:2.1</t>
+        </is>
+      </c>
+      <c r="V567" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.6</t>
+        </is>
+      </c>
+      <c r="B568" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C568" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D568" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E568" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F568" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G568" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H568" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I568" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J568" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K568" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L568" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M568" s="28" t="n">
+        <v>4184.5</v>
+      </c>
+      <c r="N568" s="28" t="n">
+        <v>4192.9</v>
+      </c>
+      <c r="O568" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P568" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q568" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:01</t>
+        </is>
+      </c>
+      <c r="R568" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:45</t>
+        </is>
+      </c>
+      <c r="S568" s="28" t="n">
+        <v>4192.9</v>
+      </c>
+      <c r="T568" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U568" s="15" t="inlineStr">
+        <is>
+          <t>1:2.2</t>
+        </is>
+      </c>
+      <c r="V568" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.7</t>
+        </is>
+      </c>
+      <c r="B569" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C569" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D569" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E569" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F569" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G569" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H569" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I569" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J569" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K569" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L569" s="28" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M569" s="28" t="n">
+        <v>4185</v>
+      </c>
+      <c r="N569" s="28" t="n">
+        <v>4193.4</v>
+      </c>
+      <c r="O569" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P569" s="6" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="Q569" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:01</t>
+        </is>
+      </c>
+      <c r="R569" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-22 22:03</t>
+        </is>
+      </c>
+      <c r="S569" s="28" t="n">
+        <v>4193.4</v>
+      </c>
+      <c r="T569" s="10" t="n">
+        <v>-8.399999999999636</v>
+      </c>
+      <c r="U569" s="15" t="inlineStr">
+        <is>
+          <t>1:2.3</t>
+        </is>
+      </c>
+      <c r="V569" s="16" t="inlineStr">
+        <is>
+          <t>-1.0R</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23#05.8</t>
+        </is>
+      </c>
+      <c r="B570" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C570" s="26" t="inlineStr">
+        <is>
+          <t>12:51 AM</t>
+        </is>
+      </c>
+      <c r="D570" s="26" t="inlineStr">
+        <is>
+          <t>2026-06-22 20:51</t>
+        </is>
+      </c>
+      <c r="E570" s="26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F570" s="27" t="n">
+        <v>4182</v>
+      </c>
+      <c r="G570" s="27" t="n">
+        <v>4184</v>
+      </c>
+      <c r="H570" s="27" t="n">
+        <v>4186</v>
+      </c>
+      <c r="I570" s="27" t="n">
+        <v>4178</v>
+      </c>
+      <c r="J570" s="27" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K570" s="27" t="n">
+        <v>4166</v>
+      </c>
+      <c r="L570" s="34" t="n">
+        <v>4166</v>
+      </c>
+      <c r="M570" s="34" t="n">
+        <v>4185.5</v>
+      </c>
+      <c r="N570" s="34" t="n">
+        <v>4193.9</v>
+      </c>
+      <c r="O570" s="35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P570" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="Q570" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-22 21:10</t>
+        </is>
+      </c>
+      <c r="R570" s="9" t="n"/>
+      <c r="S570" s="34" t="n"/>
+      <c r="T570" s="51" t="n"/>
+      <c r="U570" s="37" t="inlineStr">
+        <is>
+          <t>1:2.3</t>
+        </is>
+      </c>
+      <c r="V570" s="52" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:V554"/>
+  <autoFilter ref="A2:V570"/>
   <mergeCells count="3">
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="A1:E1"/>
